--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2019_T2_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2019_T2_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>82</t>
+    <t>78</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>11.558</t>
-  </si>
-  <si>
-    <t>(10.148)</t>
-  </si>
-  <si>
-    <t>7.610</t>
-  </si>
-  <si>
-    <t>(0.930)</t>
-  </si>
-  <si>
-    <t>4.517</t>
-  </si>
-  <si>
-    <t>(1.074)</t>
-  </si>
-  <si>
-    <t>32.995</t>
-  </si>
-  <si>
-    <t>(20.297)</t>
-  </si>
-  <si>
-    <t>1.374</t>
-  </si>
-  <si>
-    <t>(0.162)</t>
-  </si>
-  <si>
-    <t>8.585</t>
-  </si>
-  <si>
-    <t>(0.980)</t>
-  </si>
-  <si>
-    <t>8.364</t>
-  </si>
-  <si>
-    <t>(3.577)</t>
-  </si>
-  <si>
-    <t>7.183</t>
-  </si>
-  <si>
-    <t>(6.770)</t>
-  </si>
-  <si>
-    <t>46.524</t>
-  </si>
-  <si>
-    <t>(33.783)</t>
-  </si>
-  <si>
-    <t>19.607</t>
-  </si>
-  <si>
-    <t>(7.187)</t>
+    <t>1.439</t>
+  </si>
+  <si>
+    <t>(0.233)</t>
+  </si>
+  <si>
+    <t>7.910</t>
+  </si>
+  <si>
+    <t>(0.965)</t>
+  </si>
+  <si>
+    <t>4.072</t>
+  </si>
+  <si>
+    <t>(0.955)</t>
+  </si>
+  <si>
+    <t>11.897</t>
+  </si>
+  <si>
+    <t>(2.322)</t>
+  </si>
+  <si>
+    <t>1.403</t>
+  </si>
+  <si>
+    <t>(0.166)</t>
+  </si>
+  <si>
+    <t>8.949</t>
+  </si>
+  <si>
+    <t>(1.012)</t>
+  </si>
+  <si>
+    <t>4.582</t>
+  </si>
+  <si>
+    <t>(1.311)</t>
+  </si>
+  <si>
+    <t>0.401</t>
+  </si>
+  <si>
+    <t>(0.079)</t>
+  </si>
+  <si>
+    <t>12.313</t>
+  </si>
+  <si>
+    <t>(2.093)</t>
+  </si>
+  <si>
+    <t>11.685</t>
+  </si>
+  <si>
+    <t>(2.803)</t>
   </si>
   <si>
     <t>32</t>
@@ -198,7 +198,7 @@
     <t>(2.545)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-10.025</t>
-  </si>
-  <si>
-    <t>1.046</t>
-  </si>
-  <si>
-    <t>3.983*</t>
-  </si>
-  <si>
-    <t>-18.640</t>
-  </si>
-  <si>
-    <t>-0.246</t>
-  </si>
-  <si>
-    <t>-0.179</t>
-  </si>
-  <si>
-    <t>-5.476</t>
-  </si>
-  <si>
-    <t>-6.876</t>
-  </si>
-  <si>
-    <t>-30.410</t>
-  </si>
-  <si>
-    <t>-6.431</t>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>0.746</t>
+  </si>
+  <si>
+    <t>4.428**</t>
+  </si>
+  <si>
+    <t>2.457</t>
+  </si>
+  <si>
+    <t>-0.275</t>
+  </si>
+  <si>
+    <t>-0.542</t>
+  </si>
+  <si>
+    <t>-1.695</t>
+  </si>
+  <si>
+    <t>-0.095</t>
+  </si>
+  <si>
+    <t>3.802</t>
+  </si>
+  <si>
+    <t>1.491</t>
   </si>
 </sst>
 </file>
